--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132056619</v>
       </c>
       <c r="B2" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132056151</v>
       </c>
       <c r="B3" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>132056450</v>
       </c>
       <c r="B5" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>132056212</v>
       </c>
       <c r="B6" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>132056202</v>
       </c>
       <c r="B9" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>132056603</v>
       </c>
       <c r="B12" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1876,7 +1876,7 @@
         <v>132056167</v>
       </c>
       <c r="B13" t="n">
-        <v>80449</v>
+        <v>80451</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>132056492</v>
       </c>
       <c r="B15" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -1983,42 +1983,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132056266</v>
+        <v>132056492</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2026,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775178</v>
+        <v>775219</v>
       </c>
       <c r="R14" t="n">
-        <v>7150530</v>
+        <v>7150557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2070,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,6 +2079,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2093,46 +2098,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132056492</v>
+        <v>132056266</v>
       </c>
       <c r="B15" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2140,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>775219</v>
+        <v>775178</v>
       </c>
       <c r="R15" t="n">
-        <v>7150557</v>
+        <v>7150530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2181,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,7 +2190,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132056582</v>
+        <v>132056373</v>
       </c>
       <c r="B7" t="n">
-        <v>57945</v>
+        <v>57948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,16 +1227,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1249,7 +1249,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775278</v>
+        <v>775169</v>
       </c>
       <c r="R7" t="n">
-        <v>7150623</v>
+        <v>7150606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132056373</v>
+        <v>132056582</v>
       </c>
       <c r="B8" t="n">
-        <v>57948</v>
+        <v>57945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1359,7 +1359,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775169</v>
+        <v>775278</v>
       </c>
       <c r="R8" t="n">
-        <v>7150606</v>
+        <v>7150623</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1657,42 +1657,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132056258</v>
+        <v>132056603</v>
       </c>
       <c r="B11" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775192</v>
+        <v>775271</v>
       </c>
       <c r="R11" t="n">
-        <v>7150473</v>
+        <v>7150626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,17 +1738,13 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>äldre hackade hål i tallhögstubbe</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1767,42 +1763,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132056603</v>
+        <v>132056258</v>
       </c>
       <c r="B12" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775271</v>
+        <v>775192</v>
       </c>
       <c r="R12" t="n">
-        <v>7150626</v>
+        <v>7150473</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,13 +1844,17 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>äldre hackade hål i tallhögstubbe</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1983,46 +1983,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132056492</v>
+        <v>132056266</v>
       </c>
       <c r="B14" t="n">
-        <v>99098</v>
+        <v>57945</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2030,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775219</v>
+        <v>775178</v>
       </c>
       <c r="R14" t="n">
-        <v>7150557</v>
+        <v>7150530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,7 +2066,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,7 +2075,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2098,42 +2093,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132056266</v>
+        <v>132056492</v>
       </c>
       <c r="B15" t="n">
-        <v>57945</v>
+        <v>99098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2141,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>775178</v>
+        <v>775219</v>
       </c>
       <c r="R15" t="n">
-        <v>7150530</v>
+        <v>7150557</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,7 +2180,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,6 +2189,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132056619</v>
       </c>
       <c r="B2" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132056151</v>
       </c>
       <c r="B3" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>132056093</v>
       </c>
       <c r="B4" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>132056450</v>
       </c>
       <c r="B5" t="n">
-        <v>91842</v>
+        <v>91848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132056212</v>
+        <v>132056582</v>
       </c>
       <c r="B6" t="n">
-        <v>91888</v>
+        <v>57946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,30 +1122,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775197</v>
+        <v>775278</v>
       </c>
       <c r="R6" t="n">
-        <v>7150455</v>
+        <v>7150623</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,13 +1192,17 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1219,7 +1224,7 @@
         <v>132056373</v>
       </c>
       <c r="B7" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132056582</v>
+        <v>132056212</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>91894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,31 +1342,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1369,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775278</v>
+        <v>775197</v>
       </c>
       <c r="R8" t="n">
-        <v>7150623</v>
+        <v>7150455</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,17 +1411,13 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>132056202</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>132056034</v>
       </c>
       <c r="B10" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,42 +1657,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132056603</v>
+        <v>132056258</v>
       </c>
       <c r="B11" t="n">
-        <v>99098</v>
+        <v>57946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775271</v>
+        <v>775192</v>
       </c>
       <c r="R11" t="n">
-        <v>7150626</v>
+        <v>7150473</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,13 +1738,17 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre hackade hål i tallhögstubbe</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1763,42 +1767,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132056258</v>
+        <v>132056603</v>
       </c>
       <c r="B12" t="n">
-        <v>57945</v>
+        <v>99106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775192</v>
+        <v>775271</v>
       </c>
       <c r="R12" t="n">
-        <v>7150473</v>
+        <v>7150626</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,17 +1848,13 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>äldre hackade hål i tallhögstubbe</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>132056167</v>
       </c>
       <c r="B13" t="n">
-        <v>80451</v>
+        <v>80453</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>132056266</v>
       </c>
       <c r="B14" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>132056492</v>
       </c>
       <c r="B15" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132056582</v>
+        <v>132056373</v>
       </c>
       <c r="B6" t="n">
-        <v>57946</v>
+        <v>57949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,16 +1122,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1144,7 +1144,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775278</v>
+        <v>775169</v>
       </c>
       <c r="R6" t="n">
-        <v>7150623</v>
+        <v>7150606</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132056373</v>
+        <v>132056582</v>
       </c>
       <c r="B7" t="n">
-        <v>57949</v>
+        <v>57946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,16 +1232,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775169</v>
+        <v>775278</v>
       </c>
       <c r="R7" t="n">
-        <v>7150606</v>
+        <v>7150623</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1983,42 +1983,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132056266</v>
+        <v>132056492</v>
       </c>
       <c r="B14" t="n">
-        <v>57946</v>
+        <v>99106</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2026,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775178</v>
+        <v>775219</v>
       </c>
       <c r="R14" t="n">
-        <v>7150530</v>
+        <v>7150557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2070,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,6 +2079,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2093,46 +2098,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132056492</v>
+        <v>132056266</v>
       </c>
       <c r="B15" t="n">
-        <v>99106</v>
+        <v>57946</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2140,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>775219</v>
+        <v>775178</v>
       </c>
       <c r="R15" t="n">
-        <v>7150557</v>
+        <v>7150530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2181,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,7 +2190,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132056619</v>
       </c>
       <c r="B2" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132056151</v>
       </c>
       <c r="B3" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>132056093</v>
       </c>
       <c r="B4" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>132056450</v>
       </c>
       <c r="B5" t="n">
-        <v>91848</v>
+        <v>91858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132056373</v>
+        <v>132056212</v>
       </c>
       <c r="B6" t="n">
-        <v>57949</v>
+        <v>91904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,31 +1122,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775169</v>
+        <v>775197</v>
       </c>
       <c r="R6" t="n">
-        <v>7150606</v>
+        <v>7150455</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,17 +1191,13 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1224,7 +1219,7 @@
         <v>132056582</v>
       </c>
       <c r="B7" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132056212</v>
+        <v>132056373</v>
       </c>
       <c r="B8" t="n">
-        <v>91894</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,30 +1337,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1373,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775197</v>
+        <v>775169</v>
       </c>
       <c r="R8" t="n">
-        <v>7150455</v>
+        <v>7150606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,13 +1407,17 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>132056202</v>
       </c>
       <c r="B9" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>132056034</v>
       </c>
       <c r="B10" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>132056258</v>
       </c>
       <c r="B11" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>132056603</v>
       </c>
       <c r="B12" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,41 +1873,42 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132056167</v>
+        <v>132056266</v>
       </c>
       <c r="B13" t="n">
-        <v>80453</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1915,10 +1916,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775324</v>
+        <v>775178</v>
       </c>
       <c r="R13" t="n">
-        <v>7150510</v>
+        <v>7150530</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,7 +1956,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på gammal sälg med lunglav</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,7 +1965,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1983,46 +1983,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132056492</v>
+        <v>132056167</v>
       </c>
       <c r="B14" t="n">
-        <v>99106</v>
+        <v>80461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2030,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775219</v>
+        <v>775324</v>
       </c>
       <c r="R14" t="n">
-        <v>7150557</v>
+        <v>7150510</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,7 +2065,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
+          <t>på gammal sälg med lunglav</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2098,42 +2093,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132056266</v>
+        <v>132056492</v>
       </c>
       <c r="B15" t="n">
-        <v>57946</v>
+        <v>99116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2141,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>775178</v>
+        <v>775219</v>
       </c>
       <c r="R15" t="n">
-        <v>7150530</v>
+        <v>7150557</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2181,7 +2180,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2190,6 +2189,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -1657,42 +1657,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132056258</v>
+        <v>132056603</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>99116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775192</v>
+        <v>775271</v>
       </c>
       <c r="R11" t="n">
-        <v>7150473</v>
+        <v>7150626</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,17 +1738,13 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>äldre hackade hål i tallhögstubbe</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1767,42 +1763,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132056603</v>
+        <v>132056258</v>
       </c>
       <c r="B12" t="n">
-        <v>99116</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1810,10 +1806,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775271</v>
+        <v>775192</v>
       </c>
       <c r="R12" t="n">
-        <v>7150626</v>
+        <v>7150473</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,13 +1844,17 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>äldre hackade hål i tallhögstubbe</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132056619</v>
       </c>
       <c r="B2" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>132056450</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>91859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132056212</v>
+        <v>132056582</v>
       </c>
       <c r="B6" t="n">
-        <v>91904</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,30 +1122,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1153,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775197</v>
+        <v>775278</v>
       </c>
       <c r="R6" t="n">
-        <v>7150455</v>
+        <v>7150623</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1191,13 +1192,17 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1216,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132056582</v>
+        <v>132056373</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,16 +1232,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1249,7 +1254,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1259,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775278</v>
+        <v>775169</v>
       </c>
       <c r="R7" t="n">
-        <v>7150623</v>
+        <v>7150606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1304,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132056373</v>
+        <v>132056212</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,31 +1342,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1369,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775169</v>
+        <v>775197</v>
       </c>
       <c r="R8" t="n">
-        <v>7150606</v>
+        <v>7150455</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,17 +1411,13 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1439,7 +1439,7 @@
         <v>132056202</v>
       </c>
       <c r="B9" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,42 +1657,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132056603</v>
+        <v>132056258</v>
       </c>
       <c r="B11" t="n">
-        <v>99116</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>775271</v>
+        <v>775192</v>
       </c>
       <c r="R11" t="n">
-        <v>7150626</v>
+        <v>7150473</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1738,13 +1738,17 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>äldre hackade hål i tallhögstubbe</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1763,42 +1767,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132056258</v>
+        <v>132056603</v>
       </c>
       <c r="B12" t="n">
-        <v>57950</v>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1806,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>775192</v>
+        <v>775271</v>
       </c>
       <c r="R12" t="n">
-        <v>7150473</v>
+        <v>7150626</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1844,17 +1848,13 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>äldre hackade hål i tallhögstubbe</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1983,41 +1983,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132056167</v>
+        <v>132056492</v>
       </c>
       <c r="B14" t="n">
-        <v>80461</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2025,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775324</v>
+        <v>775219</v>
       </c>
       <c r="R14" t="n">
-        <v>7150510</v>
+        <v>7150557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2065,7 +2070,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>på gammal sälg med lunglav</t>
+          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,46 +2098,41 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132056492</v>
+        <v>132056167</v>
       </c>
       <c r="B15" t="n">
-        <v>99116</v>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>775219</v>
+        <v>775324</v>
       </c>
       <c r="R15" t="n">
-        <v>7150557</v>
+        <v>7150510</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
+          <t>på gammal sälg med lunglav</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132056582</v>
+        <v>132056212</v>
       </c>
       <c r="B6" t="n">
-        <v>57950</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1122,31 +1122,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775278</v>
+        <v>775197</v>
       </c>
       <c r="R6" t="n">
-        <v>7150623</v>
+        <v>7150455</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,17 +1191,13 @@
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>hack i låga</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1221,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132056373</v>
+        <v>132056582</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,16 +1227,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1254,7 +1249,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1264,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775169</v>
+        <v>775278</v>
       </c>
       <c r="R7" t="n">
-        <v>7150606</v>
+        <v>7150623</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132056212</v>
+        <v>132056373</v>
       </c>
       <c r="B8" t="n">
-        <v>91905</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1342,30 +1337,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1373,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775197</v>
+        <v>775169</v>
       </c>
       <c r="R8" t="n">
-        <v>7150455</v>
+        <v>7150606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1411,13 +1407,17 @@
           <t>2026-03-30</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132056582</v>
+        <v>132056373</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,16 +1227,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1249,7 +1249,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775278</v>
+        <v>775169</v>
       </c>
       <c r="R7" t="n">
-        <v>7150623</v>
+        <v>7150606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132056373</v>
+        <v>132056582</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1359,7 +1359,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775169</v>
+        <v>775278</v>
       </c>
       <c r="R8" t="n">
-        <v>7150606</v>
+        <v>7150623</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1873,42 +1873,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132056266</v>
+        <v>132056167</v>
       </c>
       <c r="B13" t="n">
-        <v>57950</v>
+        <v>80461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1916,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775178</v>
+        <v>775324</v>
       </c>
       <c r="R13" t="n">
-        <v>7150530</v>
+        <v>7150510</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1956,7 +1955,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>på gammal sälg med lunglav</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1965,6 +1964,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1983,46 +1983,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132056492</v>
+        <v>132056266</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2030,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775219</v>
+        <v>775178</v>
       </c>
       <c r="R14" t="n">
-        <v>7150557</v>
+        <v>7150530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2070,7 +2066,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,7 +2075,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2098,41 +2093,46 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132056167</v>
+        <v>132056492</v>
       </c>
       <c r="B15" t="n">
-        <v>80461</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2140,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>775324</v>
+        <v>775219</v>
       </c>
       <c r="R15" t="n">
-        <v>7150510</v>
+        <v>7150557</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på gammal sälg med lunglav</t>
+          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132056373</v>
+        <v>132056582</v>
       </c>
       <c r="B7" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,16 +1227,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1249,7 +1249,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775169</v>
+        <v>775278</v>
       </c>
       <c r="R7" t="n">
-        <v>7150606</v>
+        <v>7150623</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132056582</v>
+        <v>132056373</v>
       </c>
       <c r="B8" t="n">
-        <v>57950</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1359,7 +1359,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775278</v>
+        <v>775169</v>
       </c>
       <c r="R8" t="n">
-        <v>7150623</v>
+        <v>7150606</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132056619</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>132056151</v>
       </c>
       <c r="B3" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
         <v>132056093</v>
       </c>
       <c r="B4" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>132056450</v>
       </c>
       <c r="B5" t="n">
-        <v>91859</v>
+        <v>91860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>132056212</v>
       </c>
       <c r="B6" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1216,10 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132056582</v>
+        <v>132056373</v>
       </c>
       <c r="B7" t="n">
-        <v>57950</v>
+        <v>57954</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,16 +1227,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1249,7 +1249,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>bobygge</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>775278</v>
+        <v>775169</v>
       </c>
       <c r="R7" t="n">
-        <v>7150623</v>
+        <v>7150606</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132056373</v>
+        <v>132056582</v>
       </c>
       <c r="B8" t="n">
-        <v>57953</v>
+        <v>57951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,16 +1337,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1359,7 +1359,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>775169</v>
+        <v>775278</v>
       </c>
       <c r="R8" t="n">
-        <v>7150606</v>
+        <v>7150623</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>bohål i asp, ca 2 meters höjd, 4x4cm stort</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,7 +1439,7 @@
         <v>132056202</v>
       </c>
       <c r="B9" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>132056034</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>132056258</v>
       </c>
       <c r="B11" t="n">
-        <v>57950</v>
+        <v>57951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>132056603</v>
       </c>
       <c r="B12" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,41 +1873,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132056167</v>
+        <v>132056492</v>
       </c>
       <c r="B13" t="n">
-        <v>80461</v>
+        <v>99119</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1915,10 +1920,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>775324</v>
+        <v>775219</v>
       </c>
       <c r="R13" t="n">
-        <v>7150510</v>
+        <v>7150557</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1955,7 +1960,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på gammal sälg med lunglav</t>
+          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,42 +1988,41 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132056266</v>
+        <v>132056167</v>
       </c>
       <c r="B14" t="n">
-        <v>57950</v>
+        <v>80462</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2026,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>775178</v>
+        <v>775324</v>
       </c>
       <c r="R14" t="n">
-        <v>7150530</v>
+        <v>7150510</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2066,7 +2070,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>hack i död ved</t>
+          <t>på gammal sälg med lunglav</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2075,6 +2079,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2093,46 +2098,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132056492</v>
+        <v>132056266</v>
       </c>
       <c r="B15" t="n">
-        <v>99118</v>
+        <v>57951</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2140,10 +2141,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>775219</v>
+        <v>775178</v>
       </c>
       <c r="R15" t="n">
-        <v>7150557</v>
+        <v>7150530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2180,7 +2181,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ca 0,5 x 0,5 m med bladrosetter och tre överblommade ex</t>
+          <t>hack i död ved</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,7 +2190,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 23646-2025 artfynd.xlsx
+++ b/artfynd/A 23646-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056212</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056151</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056167</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056093</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056258</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056266</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056582</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056034</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056373</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1878,6 +1933,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056202</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1993,6 +2053,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056492</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056603</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,8 +2275,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132056619</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>